--- a/data/processed/name_mapping.xlsx
+++ b/data/processed/name_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,36 +431,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>周芷</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>杨周武之妻何晓初</t>
+          <t>王静</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>王静</t>
+          <t>杨周武</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>张夏天</t>
+          <t>老刘</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>王静</t>
+          <t>刘力飚</t>
         </is>
       </c>
     </row>
@@ -472,55 +472,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>杨周武之妻何晓初</t>
+          <t>何晓初</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>饶蝶</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>杨周武</t>
+          <t>何晓初控制账户</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>罗宇</t>
+          <t>周芷</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>王静</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>陈三一</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>王静</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>饶蝶</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>杨周武之妻何晓初</t>
+          <t>何晓初控制账户</t>
         </is>
       </c>
     </row>

--- a/data/processed/name_mapping.xlsx
+++ b/data/processed/name_mapping.xlsx
@@ -413,18 +413,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>假名</t>
+          <t>假名/别名/账户名</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>案件真实姓名</t>
+          <t>统一显示名</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>映射类型</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>是否自动合并</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>说明</t>
         </is>
       </c>
     </row>
@@ -439,64 +454,262 @@
           <t>王静</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>流水账户假名</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>行贿方王静的合成银行流水账户名。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>张伟</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>杨周武</t>
+          <t>王静</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>新闻/调查材料化名</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>证据5-2中“张伟（真实姓名王静）”，可进入人工确认。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>老刘</t>
+          <t>李四</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>刘力飚</t>
+          <t>杨周武</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>流水/通话账户假名</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>杨周武的合成账户或通话假名。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>曾黎</t>
+          <t>杨所长</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>何晓初</t>
+          <t>杨周武</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>职务称呼</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>同乐派出所所长杨周武。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>饶蝶</t>
+          <t>曾黎</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>何晓初控制账户</t>
+          <t>何晓初</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>马甲账户</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>何晓初控制或关联账户。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>饶蝶</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>何晓初</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>马甲账户</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>何晓初关联账户，需结合流水人工确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>周芷</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>何晓初控制账户</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>何晓初</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>马甲账户</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>何晓初关联账户，需结合流水人工确认。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>老刘</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>刘力飚</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>通话假名</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>刘力飚的合成通话假名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>赵五</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>赵五</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>工商登记名义经营者</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>营业执照经营者，不与王静自动合并；仅提示王静可能为实际控制人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>舞王歌舞厅</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>舞王俱乐部</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>场所曾用/旧称</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>建议</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>需结合工商许可、吊销材料和实际经营地址确认。</t>
         </is>
       </c>
     </row>

--- a/data/processed/name_mapping.xlsx
+++ b/data/processed/name_mapping.xlsx
@@ -419,297 +419,297 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>假名/别名/账户名</t>
+          <t>??/??/???</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>统一显示名</t>
+          <t>?????</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>映射类型</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>是否自动合并</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>??</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>??</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>王静</t>
+          <t>??</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>流水账户假名</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>行贿方王静的合成银行流水账户名。</t>
+          <t>????????????????</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>张伟</t>
+          <t>??</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>王静</t>
+          <t>??</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>新闻/调查材料化名</t>
+          <t>??/??????</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>??</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>证据5-2中“张伟（真实姓名王静）”，可进入人工确认。</t>
+          <t>??5-2??????????????????????</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>??</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>杨周武</t>
+          <t>???</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>流水/通话账户假名</t>
+          <t>??/??????</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>杨周武的合成账户或通话假名。</t>
+          <t>??????????????</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>杨所长</t>
+          <t>???</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>杨周武</t>
+          <t>???</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>职务称呼</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>同乐派出所所长杨周武。</t>
+          <t>???????????</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>曾黎</t>
+          <t>??</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>何晓初</t>
+          <t>???</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>马甲账户</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>何晓初控制或关联账户。</t>
+          <t>???????????</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>饶蝶</t>
+          <t>??</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>何晓初</t>
+          <t>???</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>马甲账户</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>??</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>何晓初关联账户，需结合流水人工确认。</t>
+          <t>??????????????????</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>周芷</t>
+          <t>??</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>何晓初</t>
+          <t>???</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>马甲账户</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>??</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>何晓初关联账户，需结合流水人工确认。</t>
+          <t>??????????????????</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>老刘</t>
+          <t>??</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>刘力飚</t>
+          <t>???</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>通话假名</t>
+          <t>????</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>刘力飚的合成通话假名。</t>
+          <t>???????????</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>赵五</t>
+          <t>??</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>赵五</t>
+          <t>??</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>工商登记名义经营者</t>
+          <t>?????????</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>营业执照经营者，不与王静自动合并；仅提示王静可能为实际控制人。</t>
+          <t>???????????????????????????????</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>舞王歌舞厅</t>
+          <t>?????</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>舞王俱乐部</t>
+          <t>?????</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>场所曾用/旧称</t>
+          <t>????/??</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>建议</t>
+          <t>??</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>需结合工商许可、吊销材料和实际经营地址确认。</t>
+          <t>??????????????????????</t>
         </is>
       </c>
     </row>
